--- a/data/trans_dic/IP25A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,14 +519,13 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -535,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -573,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -629,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -646,62 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -714,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,76</t>
+          <t>1,05; 9,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,6</t>
+          <t>2,66; 12,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 13,7</t>
+          <t>10,86; 24,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 13,88</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>5,53; 16,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,9</t>
+          <t>13,0; 26,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 17,01</t>
+          <t>0,55; 5,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 16,16</t>
+          <t>5,13; 12,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,8</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3,05; 7,33</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7,58; 13,56</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,02; 13,15</t>
+          <t>13,45; 22,89</t>
         </is>
       </c>
     </row>
@@ -786,62 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>41,92%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -854,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 29,72</t>
+          <t>20,9; 30,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,58; 36,13</t>
+          <t>28,35; 38,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,65; 47,01</t>
+          <t>38,57; 50,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,75</t>
+          <t>23,23; 31,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,83; 30,98</t>
+          <t>31,28; 41,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,56; 40,06</t>
+          <t>38,85; 49,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,24; 47,08</t>
+          <t>23,27; 30,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 19,24</t>
+          <t>30,56; 38,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,51; 28,8</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>30,68; 37,93</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>38,09; 45,12</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,61; 16,87</t>
+          <t>40,1; 47,42</t>
         </is>
       </c>
     </row>
@@ -926,62 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>43,68%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>46,16%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -994,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,03; 47,29</t>
+          <t>35,04; 49,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,83; 49,0</t>
+          <t>36,77; 50,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,3; 48,8</t>
+          <t>37,97; 50,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 26,89</t>
+          <t>42,79; 56,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,49; 53,78</t>
+          <t>38,99; 52,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,66; 51,36</t>
+          <t>44,12; 56,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,1; 55,38</t>
+          <t>40,38; 50,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 20,18</t>
+          <t>39,86; 49,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 48,98</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>39,17; 48,6</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41,81; 50,64</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>13,43; 20,7</t>
+          <t>42,94; 51,68</t>
         </is>
       </c>
     </row>
@@ -1066,62 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>42,81%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>54,31%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
+          <t>56,96%</t>
         </is>
       </c>
     </row>
@@ -1134,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,93; 60,44</t>
+          <t>50,27; 61,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,6; 51,02</t>
+          <t>40,87; 53,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,46; 63,2</t>
+          <t>52,73; 65,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 15,76</t>
+          <t>48,35; 59,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,02; 57,78</t>
+          <t>35,79; 48,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,22; 46,53</t>
+          <t>48,32; 61,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,61; 58,44</t>
+          <t>50,91; 59,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 18,1</t>
+          <t>39,59; 48,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,67; 57,7</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>38,62; 47,36</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>49,89; 58,78</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>10,03; 15,66</t>
+          <t>52,38; 61,3</t>
         </is>
       </c>
     </row>
@@ -1206,62 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -1274,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,9; 35,54</t>
+          <t>33,28; 39,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,65; 34,63</t>
+          <t>32,47; 39,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,76; 42,71</t>
+          <t>41,56; 48,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,79; 16,25</t>
+          <t>35,01; 41,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,65; 36,39</t>
+          <t>33,47; 39,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,91; 35,73</t>
+          <t>42,34; 48,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,47; 44,47</t>
+          <t>35,01; 39,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,14</t>
+          <t>33,91; 38,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,16; 35,08</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30,31; 34,21</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>38,1; 42,5</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,08; 15,71</t>
+          <t>42,89; 47,56</t>
         </is>
       </c>
     </row>
@@ -1342,15 +1171,966 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5368</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12042</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14717</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2526</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14066</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>26759</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>565; 4989</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2204; 10165</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7863; 17618</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3966</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4843; 14328</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9926; 20406</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>602; 5917</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8741; 21126</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20008; 34056</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>62990</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74655</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>87870</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66536</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95666</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>108567</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>129526</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>170321</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>196436</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>51511; 74184</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>64796; 87818</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>77119; 100360</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56335; 77472</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>83062; 110539</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>96375; 122393</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>113767; 146958</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>150995; 187983</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>179652; 212466</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>51795</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67101</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>80805</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>66684</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70750</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93436</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>118478</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>137850</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>174241</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>43959; 62070</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56718; 77439</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69570; 91728</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57628; 76137</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>60667; 81801</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>82164; 104986</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>105055; 131273</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>123517; 152480</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>158622; 190905</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>106403</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>77274</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>98318</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>107604</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73116</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90343</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>214007</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>150390</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>188661</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>94535; 115908</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67953; 89248</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>87947; 108819</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96206; 118801</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>62395; 84247</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>79461; 100763</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>197031; 229345</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>134859; 165215</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>173499; 203051</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>223065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>224398</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>279034</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>464536</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>472627</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>586097</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>204283; 241902</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>205233; 246614</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>258655; 300004</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>221272; 262514</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>228621; 267905</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>285822; 328199</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>436116; 490173</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>445925; 503374</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>556494; 617007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_dic/IP25A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,28</t>
+          <t>1,06; 9,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 12,26</t>
+          <t>3,14; 12,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 24,33</t>
+          <t>10,76; 24,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 16,36</t>
+          <t>5,71; 16,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 26,73</t>
+          <t>12,86; 27,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,4</t>
+          <t>0,55; 4,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 12,39</t>
+          <t>5,32; 12,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 22,89</t>
+          <t>13,29; 23,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 30,1</t>
+          <t>20,98; 30,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,35; 38,42</t>
+          <t>27,41; 37,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,57; 50,19</t>
+          <t>38,83; 49,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 31,95</t>
+          <t>23,24; 32,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,28; 41,63</t>
+          <t>31,32; 41,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,85; 49,34</t>
+          <t>37,93; 48,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 30,06</t>
+          <t>23,11; 29,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,56; 38,05</t>
+          <t>31,11; 38,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,1; 47,42</t>
+          <t>39,82; 47,37</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,04; 49,47</t>
+          <t>34,45; 49,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,77; 50,2</t>
+          <t>37,1; 49,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,97; 50,06</t>
+          <t>37,67; 49,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,79; 56,53</t>
+          <t>42,83; 57,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,99; 52,57</t>
+          <t>39,58; 52,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,12; 56,38</t>
+          <t>44,12; 56,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,38; 50,46</t>
+          <t>41,19; 50,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,86; 49,21</t>
+          <t>39,53; 48,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,94; 51,68</t>
+          <t>42,39; 51,18</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,27; 61,63</t>
+          <t>50,76; 62,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,87; 53,67</t>
+          <t>39,63; 53,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,73; 65,24</t>
+          <t>52,66; 65,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,35; 59,71</t>
+          <t>48,53; 59,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,79; 48,33</t>
+          <t>36,31; 48,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,32; 61,28</t>
+          <t>47,61; 60,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,91; 59,26</t>
+          <t>50,96; 59,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,59; 48,51</t>
+          <t>40,03; 48,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,38; 61,3</t>
+          <t>52,53; 61,55</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 39,41</t>
+          <t>33,1; 39,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,47; 39,02</t>
+          <t>32,37; 38,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,56; 48,2</t>
+          <t>41,77; 48,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,01; 41,54</t>
+          <t>34,95; 41,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,47; 39,22</t>
+          <t>33,46; 39,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,34; 48,62</t>
+          <t>42,2; 48,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,01; 39,35</t>
+          <t>35,17; 39,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,91; 38,28</t>
+          <t>33,72; 37,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,89; 47,56</t>
+          <t>43,1; 47,51</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>565; 4989</t>
+          <t>567; 5186</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2204; 10165</t>
+          <t>2605; 10142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7863; 17618</t>
+          <t>7791; 17734</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3966</t>
+          <t>0; 3671</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4843; 14328</t>
+          <t>5001; 14544</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9926; 20406</t>
+          <t>9818; 21024</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>602; 5917</t>
+          <t>600; 5383</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8741; 21126</t>
+          <t>9079; 20661</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20008; 34056</t>
+          <t>19766; 34867</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51511; 74184</t>
+          <t>51714; 74127</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64796; 87818</t>
+          <t>62649; 86807</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77119; 100360</t>
+          <t>77650; 99558</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56335; 77472</t>
+          <t>56361; 77853</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83062; 110539</t>
+          <t>83178; 110589</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96375; 122393</t>
+          <t>94090; 120182</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>113767; 146958</t>
+          <t>112981; 145612</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>150995; 187983</t>
+          <t>153696; 189616</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>179652; 212466</t>
+          <t>178414; 212228</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43959; 62070</t>
+          <t>43224; 61511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56718; 77439</t>
+          <t>57229; 77107</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69570; 91728</t>
+          <t>69025; 90952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57628; 76137</t>
+          <t>57689; 76767</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>60667; 81801</t>
+          <t>61594; 81091</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82164; 104986</t>
+          <t>82153; 105283</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>105055; 131273</t>
+          <t>107161; 131307</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>123517; 152480</t>
+          <t>122491; 151794</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>158622; 190905</t>
+          <t>156597; 189089</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94535; 115908</t>
+          <t>95466; 118110</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67953; 89248</t>
+          <t>65893; 88128</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87947; 108819</t>
+          <t>87834; 108547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96206; 118801</t>
+          <t>96556; 118397</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62395; 84247</t>
+          <t>63299; 84234</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79461; 100763</t>
+          <t>78282; 99985</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>197031; 229345</t>
+          <t>197226; 230036</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>134859; 165215</t>
+          <t>136336; 165614</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>173499; 203051</t>
+          <t>173987; 203872</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>204283; 241902</t>
+          <t>203162; 242286</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>205233; 246614</t>
+          <t>204560; 244649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>258655; 300004</t>
+          <t>259939; 298730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>221272; 262514</t>
+          <t>220854; 261072</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>228621; 267905</t>
+          <t>228526; 269667</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>285822; 328199</t>
+          <t>284906; 329572</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>436116; 490173</t>
+          <t>438107; 491761</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>445925; 503374</t>
+          <t>443391; 498740</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>556494; 617007</t>
+          <t>559183; 616350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6,47%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,65</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 12,23</t>
+          <t>5,24; 16,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 24,49</t>
+          <t>12,99; 27,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>1,05; 9,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 16,61</t>
+          <t>3,1; 12,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 27,54</t>
+          <t>11,15; 25,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,91</t>
+          <t>0,57; 5,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,12</t>
+          <t>5,29; 12,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 23,44</t>
+          <t>13,51; 23,72</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27,44%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>25,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>32,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>43,95%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,03%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,98; 30,07</t>
+          <t>22,85; 31,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,41; 37,98</t>
+          <t>31,08; 41,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,83; 49,79</t>
+          <t>37,99; 48,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,24; 32,11</t>
+          <t>21,19; 30,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,32; 41,65</t>
+          <t>27,68; 38,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,93; 48,45</t>
+          <t>38,42; 49,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,11; 29,78</t>
+          <t>23,23; 29,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,11; 38,38</t>
+          <t>31,01; 38,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,82; 47,37</t>
+          <t>40,34; 47,5</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45,47%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50,18%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>41,28%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>43,5%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>44,1%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>45,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,45; 49,03</t>
+          <t>42,6; 56,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,1; 49,99</t>
+          <t>39,09; 52,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,67; 49,64</t>
+          <t>43,76; 55,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,83; 57,0</t>
+          <t>34,21; 48,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,58; 52,11</t>
+          <t>35,85; 49,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,12; 56,54</t>
+          <t>37,78; 49,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,19; 50,47</t>
+          <t>40,52; 50,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,53; 48,99</t>
+          <t>40,07; 49,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,39; 51,18</t>
+          <t>43,01; 51,66</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41,94%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54,94%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>56,58%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>46,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>58,95%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,76; 62,81</t>
+          <t>48,73; 59,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,63; 53,0</t>
+          <t>35,88; 48,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,66; 65,08</t>
+          <t>48,88; 61,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,53; 59,51</t>
+          <t>49,93; 62,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,31; 48,32</t>
+          <t>40,09; 52,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,61; 60,8</t>
+          <t>52,4; 65,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,96; 59,44</t>
+          <t>50,91; 59,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,03; 48,62</t>
+          <t>40,26; 48,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,53; 61,55</t>
+          <t>52,81; 61,42</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>36,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>35,51%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>44,83%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,48</t>
+          <t>35,15; 41,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,37; 38,71</t>
+          <t>33,42; 39,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,77; 48,0</t>
+          <t>42,36; 48,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,95; 41,31</t>
+          <t>33,18; 39,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,46; 39,48</t>
+          <t>32,33; 39,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,2; 48,82</t>
+          <t>41,9; 48,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,17; 39,48</t>
+          <t>35,16; 39,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,72; 37,93</t>
+          <t>33,89; 38,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 47,51</t>
+          <t>43,07; 47,32</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14717</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1878</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>5368</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>12042</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14717</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>567; 5186</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2605; 10142</t>
+          <t>4591; 14141</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7791; 17734</t>
+          <t>9919; 20926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>562; 5267</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5001; 14544</t>
+          <t>2571; 10147</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9818; 21024</t>
+          <t>8070; 18255</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>600; 5383</t>
+          <t>621; 5755</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9079; 20661</t>
+          <t>9015; 21236</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19766; 34867</t>
+          <t>20099; 35283</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66536</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>95666</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108567</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>62990</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>74655</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>87870</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66536</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95666</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>108567</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51714; 74127</t>
+          <t>55393; 77111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62649; 86807</t>
+          <t>82515; 109266</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77650; 99558</t>
+          <t>94249; 120818</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56361; 77853</t>
+          <t>52222; 74770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83178; 110589</t>
+          <t>63262; 86921</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94090; 120182</t>
+          <t>76821; 98754</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>112981; 145612</t>
+          <t>113561; 146050</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>153696; 189616</t>
+          <t>153224; 187931</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178414; 212228</t>
+          <t>180710; 212819</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>66684</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70750</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>93436</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>51795</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>67101</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>80805</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66684</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70750</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93436</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43224; 61511</t>
+          <t>57381; 76516</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57229; 77107</t>
+          <t>60831; 82263</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69025; 90952</t>
+          <t>81479; 104010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57689; 76767</t>
+          <t>42920; 60862</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61594; 81091</t>
+          <t>55296; 76012</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82153; 105283</t>
+          <t>69219; 90937</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>107161; 131307</t>
+          <t>105403; 130937</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>122491; 151794</t>
+          <t>124168; 152312</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>156597; 189089</t>
+          <t>158901; 190840</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>139</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107604</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73116</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90343</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>106403</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>77274</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>98318</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>107604</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73116</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90343</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95466; 118110</t>
+          <t>96966; 118743</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65893; 88128</t>
+          <t>62550; 83672</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87834; 108547</t>
+          <t>80378; 100742</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96556; 118397</t>
+          <t>93906; 116787</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63299; 84234</t>
+          <t>66654; 87878</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78282; 99985</t>
+          <t>87390; 108930</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>197226; 230036</t>
+          <t>197025; 229366</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>136336; 165614</t>
+          <t>137142; 164639</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>173987; 203872</t>
+          <t>174919; 203447</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>412</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>223065</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>224398</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>279034</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>241471</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>248229</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>307063</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>203162; 242286</t>
+          <t>222136; 262108</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>204560; 244649</t>
+          <t>228270; 270779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>259939; 298730</t>
+          <t>285940; 329699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>220854; 261072</t>
+          <t>203647; 241490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>228526; 269667</t>
+          <t>204349; 246544</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>284906; 329572</t>
+          <t>260763; 300181</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>438107; 491761</t>
+          <t>438009; 492547</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>443391; 498740</t>
+          <t>445637; 501424</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>559183; 616350</t>
+          <t>558745; 613965</t>
         </is>
       </c>
     </row>
